--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/582e05b6e79a01d8/Documents/University/Warwick/StudyNotes/Semester2/Alternatives/Groupwork/CBACorrelation/CBA-Correlation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{5822DA91-C8C3-4E2D-A598-57A67CDD5B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D9678E9-BA0F-40D4-B387-F758F4CD2002}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{5822DA91-C8C3-4E2D-A598-57A67CDD5B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{297E72E4-ADCA-46A6-8109-BDD0265AE0DC}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{59762D76-5CB8-40FC-A638-C06EA1521422}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{59762D76-5CB8-40FC-A638-C06EA1521422}"/>
   </bookViews>
   <sheets>
     <sheet name="ARBIX" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -216,7 +216,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2693,7 +2692,7 @@
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A177" s="7" t="s">
+      <c r="A177" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B177" s="5">

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/582e05b6e79a01d8/Documents/University/Warwick/StudyNotes/Semester2/Alternatives/Groupwork/CBACorrelation/CBA-Correlation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{5822DA91-C8C3-4E2D-A598-57A67CDD5B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{297E72E4-ADCA-46A6-8109-BDD0265AE0DC}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{5822DA91-C8C3-4E2D-A598-57A67CDD5B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{231AC4F9-E3D5-49B9-9051-79FB173E58D1}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{59762D76-5CB8-40FC-A638-C06EA1521422}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{59762D76-5CB8-40FC-A638-C06EA1521422}"/>
   </bookViews>
   <sheets>
     <sheet name="ARBIX" sheetId="1" r:id="rId1"/>
